--- a/backend/data/financials_by_company/000572.SZ.xlsx
+++ b/backend/data/financials_by_company/000572.SZ.xlsx
@@ -3895,192 +3895,192 @@
       </c>
       <c r="DD1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
         <is>
           <t>shortName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Haima Automobile Co.,Ltd, together with its subsidiaries, engages in the research, development, manufacture, sale, and financial service of automobiles and powertrains in China and internationally. The company offers basic passenger cars, sports utility vehicles, multi-purpose passenger cars, and electric vehicles. It also provides leasing, processing, and after-sales services. In addition, the company engages in technology promotion and application services. It exports its products to approximately 20 countries and regions, including Egypt, Chile, the Philippines, and Vietnam. The company was formerly known as Haima Automobile Group Co.,Ltd and changed its name to Haima Automobile Co.,Ltd in June 2019. Haima Automobile Co.,Ltd was founded in 1988 and is based in Haikou, China.</t>
+          <t>Haima Automobile Co.,Ltd, together with its subsidiaries, engages in the research, development, manufacture, sale, and financial service of automobiles and powertrains in China and internationally. The company offers passenger cars, multi-purpose passenger cars, and electric vehicles. It also provides leasing, processing, and after-sales services. In addition, the company engages in technology promotion and application services. It exports its products to approximately 20 countries and regions, including Egypt, Chile, the Philippines, and Vietnam. The company was formerly known as Haima Automobile Group Co.,Ltd and changed its name to Haima Automobile Co.,Ltd in June 2019. Haima Automobile Co.,Ltd was founded in 1988 and is based in Haikou, China.</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4185,28 +4185,28 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>4.06</v>
+        <v>4.15</v>
       </c>
       <c r="V2" t="n">
-        <v>4.09</v>
+        <v>3.84</v>
       </c>
       <c r="W2" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="X2" t="n">
-        <v>4.06</v>
+        <v>4.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.06</v>
+        <v>4.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.09</v>
+        <v>3.84</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.06</v>
+        <v>4.11</v>
       </c>
       <c r="AC2" t="n">
         <v>1466985600</v>
@@ -4215,31 +4215,31 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.416</v>
+        <v>0.436</v>
       </c>
       <c r="AF2" t="n">
-        <v>28.571428</v>
+        <v>27.785715</v>
       </c>
       <c r="AG2" t="n">
-        <v>49776900</v>
+        <v>148707099</v>
       </c>
       <c r="AH2" t="n">
-        <v>49776900</v>
+        <v>148707099</v>
       </c>
       <c r="AI2" t="n">
-        <v>54433615</v>
+        <v>40390585</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40549371</v>
+        <v>40157678</v>
       </c>
       <c r="AK2" t="n">
-        <v>40549371</v>
+        <v>40157678</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="AM2" t="n">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4248,13 +4248,13 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>6578545664</v>
+        <v>6397635584</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6677223889</v>
+        <v>6200279326</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AS2" t="n">
         <v>12.03</v>
@@ -4266,13 +4266,13 @@
         <v>1.198224</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.6438344</v>
+        <v>3.543629</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.0774</v>
+        <v>4.7316</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.7173</v>
+        <v>6.6526</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4289,19 +4289,19 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>6885905408</v>
+        <v>6704995328</v>
       </c>
       <c r="BD2" t="n">
         <v>-0.0832</v>
       </c>
       <c r="BE2" t="n">
-        <v>1070296493</v>
+        <v>1077993392</v>
       </c>
       <c r="BF2" t="n">
         <v>1644636426</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.37333</v>
+        <v>0.3657</v>
       </c>
       <c r="BH2" t="n">
         <v>0.008710000000000001</v>
@@ -4313,7 +4313,7 @@
         <v>0.958</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.1753654</v>
+        <v>4.060543</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4342,16 +4342,16 @@
         <v>1188777600</v>
       </c>
       <c r="BT2" t="n">
-        <v>3.814</v>
+        <v>3.714</v>
       </c>
       <c r="BU2" t="n">
-        <v>161.897</v>
+        <v>157.643</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.043701768</v>
+        <v>-0.08388519</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BX2" t="n">
         <v>0.05</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="CA2" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
@@ -4466,62 +4466,60 @@
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DD2" t="n">
-        <v>-1.4778311</v>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Haima Automobile Co.,Ltd</t>
+        </is>
       </c>
       <c r="DE2" t="n">
-        <v>4</v>
-      </c>
-      <c r="DF2" t="inlineStr">
+        <v>-6.26506</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="DG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>776309400000</v>
+      </c>
+      <c r="DI2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DG2" t="n">
-        <v>1782111897</v>
-      </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DJ2" t="n">
+        <v>1783062291</v>
+      </c>
+      <c r="DK2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>finmb_11381883</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DL2" t="n">
+      <c r="DO2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>Haima Automobile Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
         </is>
       </c>
       <c r="DQ2" t="b">
@@ -4529,21 +4527,23 @@
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>HAIMA AUTOMOBILE CO LTD</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
+          <t>Haima Automobile Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
         <v>0</v>
       </c>
-      <c r="DT2" t="n">
-        <v>776309400000</v>
-      </c>
       <c r="DU2" t="n">
-        <v>-0.059999943</v>
+        <v>-0.26</v>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>3.86 - 4.06</t>
+          <t>3.8 - 4.11</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
@@ -4552,27 +4552,27 @@
         </is>
       </c>
       <c r="DX2" t="n">
-        <v>54433615</v>
+        <v>40390585</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.29999995</v>
+        <v>0.31000018</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.08108107000000001</v>
+        <v>0.086592235</v>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>3.7 - 12.03</t>
+          <t>3.58 - 12.03</t>
         </is>
       </c>
       <c r="EB2" t="n">
-        <v>-8.029999999999999</v>
+        <v>-8.139999</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0.66749793</v>
+        <v>-0.6766417</v>
       </c>
       <c r="ED2" t="n">
-        <v>4.370177</v>
+        <v>-8.388519000000001</v>
       </c>
       <c r="EE2" t="n">
         <v>1619693940</v>
@@ -4587,16 +4587,16 @@
         <v>0.14</v>
       </c>
       <c r="EI2" t="n">
-        <v>-1.0774002</v>
+        <v>-0.8415997</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.21219525</v>
+        <v>-0.17786789</v>
       </c>
       <c r="EK2" t="n">
-        <v>-2.7173</v>
+        <v>-2.7625997</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0.40452266</v>
+        <v>-0.4152662</v>
       </c>
       <c r="EM2" t="n">
         <v>15</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>Haima Automobile Co.,Ltd</t>
+          <t>HAIMA AUTOMOBILE CO LTD</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr"/>
